--- a/public/downloads/templates/listing-audit-checklist.xlsx
+++ b/public/downloads/templates/listing-audit-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Listing Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listing Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -545,6 +545,7 @@
       </c>
       <c r="B3" s="3" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -974,6 +975,7 @@
       <c r="D37" s="9" t="inlineStr"/>
       <c r="E37" s="9" t="inlineStr"/>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
@@ -1012,6 +1014,13 @@
       <c r="B42">
         <f>COUNTIFS(C6:C37,"Fail",D6:D37,"High")</f>
         <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Project Amazon PH Academy — Download Center</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1037,5 +1046,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>